--- a/results/Int Task Remove ACC -0.7/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.7/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.005872884982739624</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03037429861391548</v>
+        <v>0.03037732533284934</v>
       </c>
       <c r="F3" t="n">
         <v>0.002184021847673482</v>
@@ -1166,25 +1166,25 @@
         <v>0.02170738218569015</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.001517985530107969</v>
+        <v>-0.00150932915830912</v>
       </c>
       <c r="I3" t="n">
-        <v>8.797460967170046e-05</v>
+        <v>8.535860642285952e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0446318325444945</v>
+        <v>0.04462877630977567</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02369521623079025</v>
+        <v>0.02369225589923312</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02369827158941214</v>
+        <v>0.02370418090357028</v>
       </c>
       <c r="M3" t="n">
         <v>0.01620193060290426</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04007008167121733</v>
+        <v>0.04007302891554389</v>
       </c>
       <c r="O3" t="n">
         <v>0.02040442844032075</v>
@@ -1196,7 +1196,7 @@
         <v>0.01600343528415791</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01558708490807644</v>
+        <v>0.01559881462059541</v>
       </c>
       <c r="S3" t="n">
         <v>0.2945550448381226</v>
@@ -1208,7 +1208,7 @@
         <v>0.1195994144672543</v>
       </c>
       <c r="V3" t="n">
-        <v>9.388827488078901e-05</v>
+        <v>0.0001028775228373169</v>
       </c>
       <c r="W3" t="n">
         <v>0.009002547139726124</v>
@@ -1223,7 +1223,7 @@
         <v>0.002661589083606499</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03470530660855772</v>
+        <v>0.03471121504661891</v>
       </c>
       <c r="AB3" t="n">
         <v>0.001387737771559038</v>
@@ -1304,7 +1304,7 @@
         <v>0.00666491367052168</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.006484855965215755</v>
+        <v>0.006481908720889201</v>
       </c>
       <c r="BC3" t="n">
         <v>-9.507847258011238e-06</v>
@@ -1319,7 +1319,7 @@
         <v>0.01421942358017777</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.004756638680777837</v>
+        <v>0.004762547100275621</v>
       </c>
       <c r="BH3" t="n">
         <v>0.0003456636822469416</v>
@@ -1340,7 +1340,7 @@
         <v>0.02622094197166485</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.006661939250533579</v>
+        <v>0.00666491367052168</v>
       </c>
       <c r="BO3" t="n">
         <v>0.02026641669076991</v>
@@ -1364,7 +1364,7 @@
         <v>0.04382902471669708</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.004557046064061585</v>
+        <v>0.004554097081460583</v>
       </c>
       <c r="BW3" t="n">
         <v>0.008282814873336005</v>
@@ -1428,7 +1428,7 @@
         <v>0.01145012447400461</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0326977332214976</v>
+        <v>0.03269699818739584</v>
       </c>
       <c r="F4" t="n">
         <v>0.002920908574377343</v>
@@ -1437,25 +1437,25 @@
         <v>0.05468928294964336</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002947346365568621</v>
+        <v>0.002936356107886548</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001067635825532753</v>
+        <v>0.001074427549323416</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04427809925961074</v>
+        <v>0.04428233639547005</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01292452383317492</v>
+        <v>0.01292359617584792</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01291418746466358</v>
+        <v>0.01291396756972851</v>
       </c>
       <c r="M4" t="n">
         <v>0.03239192947161385</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04063808109722671</v>
+        <v>0.04063619503031831</v>
       </c>
       <c r="O4" t="n">
         <v>0.02974371847460855</v>
@@ -1467,7 +1467,7 @@
         <v>0.02031017484773797</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01792230652482349</v>
+        <v>0.01791754958206224</v>
       </c>
       <c r="S4" t="n">
         <v>0.1032683491624796</v>
@@ -1479,7 +1479,7 @@
         <v>0.05451432125979587</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001065160617984793</v>
+        <v>0.00107292258637669</v>
       </c>
       <c r="W4" t="n">
         <v>0.02960615851271703</v>
@@ -1494,7 +1494,7 @@
         <v>0.01305070478122668</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03088892562141527</v>
+        <v>0.03088419839907405</v>
       </c>
       <c r="AB4" t="n">
         <v>0.002761503144583464</v>
@@ -1575,7 +1575,7 @@
         <v>0.008704581431167679</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01477808628566346</v>
+        <v>0.0147795718627242</v>
       </c>
       <c r="BC4" t="n">
         <v>0.0006496816510989949</v>
@@ -1590,7 +1590,7 @@
         <v>0.02479461278151418</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.02423991543767897</v>
+        <v>0.02423636988020874</v>
       </c>
       <c r="BH4" t="n">
         <v>0.000935505780414492</v>
@@ -1611,7 +1611,7 @@
         <v>0.02702221192345177</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.008704350194535184</v>
+        <v>0.008704581431167679</v>
       </c>
       <c r="BO4" t="n">
         <v>0.02742626468394797</v>
@@ -1635,7 +1635,7 @@
         <v>0.0447387708633238</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01937947570181254</v>
+        <v>0.01938458068038401</v>
       </c>
       <c r="BW4" t="n">
         <v>0.02613627851621273</v>
@@ -1708,13 +1708,13 @@
         <v>-0.0133967156439066</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.007433016421780414</v>
+        <v>-0.007404206280610726</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.001444149720011745</v>
+        <v>-0.001473622163277288</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01060513447432767</v>
+        <v>-0.01063569682151593</v>
       </c>
       <c r="K5" t="n">
         <v>-0.00375850843444806</v>
@@ -1906,7 +1906,7 @@
         <v>-0.06554671382257585</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.02562665880271312</v>
+        <v>-0.02565614862872314</v>
       </c>
       <c r="BW5" t="n">
         <v>-0.04966086700088472</v>
@@ -1982,7 +1982,7 @@
         <v>-0.003032696020484479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0004155335051602344</v>
+        <v>-0.0003933375892087698</v>
       </c>
       <c r="J6" t="n">
         <v>0.01509267494420046</v>
@@ -1991,13 +1991,13 @@
         <v>0.01602681938410345</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01602681938410345</v>
+        <v>0.01603419184060596</v>
       </c>
       <c r="M6" t="n">
         <v>-0.003645962159384408</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01868160838423417</v>
+        <v>0.01870371271668332</v>
       </c>
       <c r="O6" t="n">
         <v>0.003122044731798476</v>
@@ -2009,7 +2009,7 @@
         <v>0.005242907033318573</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002765967033526753</v>
+        <v>0.002802859828276216</v>
       </c>
       <c r="S6" t="n">
         <v>0.2532194299970584</v>
@@ -2036,7 +2036,7 @@
         <v>-0.005342995742301584</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01523069622563455</v>
+        <v>0.01523809486428504</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0004069974037743535</v>
@@ -2117,7 +2117,7 @@
         <v>0.0001794071762870275</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.0009583889255230265</v>
+        <v>-0.0009657570363394124</v>
       </c>
       <c r="BC6" t="n">
         <v>-0.0004067618652026733</v>
@@ -2250,7 +2250,7 @@
         <v>0.00519781990208556</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0008848172222553796</v>
+        <v>-0.0008550730223743586</v>
       </c>
       <c r="I7" t="n">
         <v>-0.0001180899827373572</v>
@@ -2259,10 +2259,10 @@
         <v>0.02799200438493657</v>
       </c>
       <c r="K7" t="n">
+        <v>0.0253156322393156</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.02533043389710127</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.0253156322393156</v>
       </c>
       <c r="M7" t="n">
         <v>0.01463502598476664</v>
@@ -2512,7 +2512,7 @@
         <v>0.009667835795490395</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04048926962965924</v>
+        <v>0.04049647216495166</v>
       </c>
       <c r="F8" t="n">
         <v>0.00441173768307066</v>
@@ -2521,10 +2521,10 @@
         <v>0.01664353460800519</v>
       </c>
       <c r="H8" t="n">
-        <v>0.000373419100349659</v>
+        <v>0.0003655845657210138</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006966535504257077</v>
+        <v>0.0006822484798408579</v>
       </c>
       <c r="J8" t="n">
         <v>0.07773980348720409</v>
@@ -2551,7 +2551,7 @@
         <v>0.01554052629052733</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02237997224401323</v>
+        <v>0.02240157984989051</v>
       </c>
       <c r="S8" t="n">
         <v>0.3644490880758826</v>
@@ -2563,7 +2563,7 @@
         <v>0.1507046894235935</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0006966535504257077</v>
+        <v>0.0007261642356288955</v>
       </c>
       <c r="W8" t="n">
         <v>0.03109551075958515</v>
@@ -2695,7 +2695,7 @@
         <v>0.04954154661112474</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.01070033783730476</v>
+        <v>0.01070777388727502</v>
       </c>
       <c r="BO8" t="n">
         <v>0.02542706109068594</v>
@@ -2783,7 +2783,7 @@
         <v>0.02507051081165781</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09289113622843544</v>
+        <v>0.09286139202855441</v>
       </c>
       <c r="F9" t="n">
         <v>0.007296898079763625</v>
